--- a/public/exel/sns_highschool.xlsx
+++ b/public/exel/sns_highschool.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sbfp_ao_system\public\exel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC7F4A55-40D2-4212-A90D-F84FA25601EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F727526-3107-4C64-8A49-C56540BE2C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A97BA7C1-031B-4AE1-ABEF-59888A293735}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="37">
   <si>
     <t>Department of Education</t>
   </si>
@@ -149,6 +149,15 @@
       </rPr>
       <t>SY  2025 -2026</t>
     </r>
+  </si>
+  <si>
+    <t>Approved by :</t>
+  </si>
+  <si>
+    <t>(School Head Nme)</t>
+  </si>
+  <si>
+    <t>School Head</t>
   </si>
 </sst>
 </file>
@@ -981,13 +990,53 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1008,7 +1057,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1017,52 +1065,13 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1456,149 +1465,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A1" s="51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-      <c r="D1" s="52"/>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="52"/>
-      <c r="I1" s="52"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-      <c r="Q1" s="52"/>
-      <c r="R1" s="52"/>
-      <c r="S1" s="52"/>
-      <c r="T1" s="52"/>
-      <c r="U1" s="52"/>
-      <c r="V1" s="52"/>
-      <c r="W1" s="52"/>
-      <c r="X1" s="52"/>
-      <c r="Y1" s="52"/>
+      <c r="A1" s="50" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51"/>
+      <c r="H1" s="51"/>
+      <c r="I1" s="51"/>
+      <c r="J1" s="51"/>
+      <c r="K1" s="51"/>
+      <c r="L1" s="51"/>
+      <c r="M1" s="51"/>
+      <c r="N1" s="51"/>
+      <c r="O1" s="51"/>
+      <c r="P1" s="51"/>
+      <c r="Q1" s="51"/>
+      <c r="R1" s="51"/>
+      <c r="S1" s="51"/>
+      <c r="T1" s="51"/>
+      <c r="U1" s="51"/>
+      <c r="V1" s="51"/>
+      <c r="W1" s="51"/>
+      <c r="X1" s="51"/>
+      <c r="Y1" s="51"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="52"/>
-      <c r="C2" s="52"/>
-      <c r="D2" s="52"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="52"/>
-      <c r="G2" s="52"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
-      <c r="J2" s="52"/>
-      <c r="K2" s="52"/>
-      <c r="L2" s="52"/>
-      <c r="M2" s="52"/>
-      <c r="N2" s="52"/>
-      <c r="O2" s="52"/>
-      <c r="P2" s="52"/>
-      <c r="Q2" s="52"/>
-      <c r="R2" s="52"/>
-      <c r="S2" s="52"/>
-      <c r="T2" s="52"/>
-      <c r="U2" s="52"/>
-      <c r="V2" s="52"/>
-      <c r="W2" s="52"/>
-      <c r="X2" s="52"/>
-      <c r="Y2" s="52"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="51"/>
+      <c r="K2" s="51"/>
+      <c r="L2" s="51"/>
+      <c r="M2" s="51"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="51"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="51"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="51"/>
+      <c r="U2" s="51"/>
+      <c r="V2" s="51"/>
+      <c r="W2" s="51"/>
+      <c r="X2" s="51"/>
+      <c r="Y2" s="51"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="52"/>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="52"/>
-      <c r="O3" s="52"/>
-      <c r="P3" s="52"/>
-      <c r="Q3" s="52"/>
-      <c r="R3" s="52"/>
-      <c r="S3" s="52"/>
-      <c r="T3" s="52"/>
-      <c r="U3" s="52"/>
-      <c r="V3" s="52"/>
-      <c r="W3" s="52"/>
-      <c r="X3" s="52"/>
-      <c r="Y3" s="52"/>
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
+      <c r="N3" s="51"/>
+      <c r="O3" s="51"/>
+      <c r="P3" s="51"/>
+      <c r="Q3" s="51"/>
+      <c r="R3" s="51"/>
+      <c r="S3" s="51"/>
+      <c r="T3" s="51"/>
+      <c r="U3" s="51"/>
+      <c r="V3" s="51"/>
+      <c r="W3" s="51"/>
+      <c r="X3" s="51"/>
+      <c r="Y3" s="51"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A4" s="72" t="s">
+      <c r="A4" s="52" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="52"/>
-      <c r="C4" s="52"/>
-      <c r="D4" s="52"/>
-      <c r="E4" s="52"/>
-      <c r="F4" s="52"/>
-      <c r="G4" s="52"/>
-      <c r="H4" s="52"/>
-      <c r="I4" s="52"/>
-      <c r="J4" s="52"/>
-      <c r="K4" s="52"/>
-      <c r="L4" s="52"/>
-      <c r="M4" s="52"/>
-      <c r="N4" s="52"/>
-      <c r="O4" s="52"/>
-      <c r="P4" s="52"/>
-      <c r="Q4" s="52"/>
-      <c r="R4" s="52"/>
-      <c r="S4" s="52"/>
-      <c r="T4" s="52"/>
-      <c r="U4" s="52"/>
-      <c r="V4" s="52"/>
-      <c r="W4" s="52"/>
-      <c r="X4" s="52"/>
-      <c r="Y4" s="52"/>
+      <c r="B4" s="51"/>
+      <c r="C4" s="51"/>
+      <c r="D4" s="51"/>
+      <c r="E4" s="51"/>
+      <c r="F4" s="51"/>
+      <c r="G4" s="51"/>
+      <c r="H4" s="51"/>
+      <c r="I4" s="51"/>
+      <c r="J4" s="51"/>
+      <c r="K4" s="51"/>
+      <c r="L4" s="51"/>
+      <c r="M4" s="51"/>
+      <c r="N4" s="51"/>
+      <c r="O4" s="51"/>
+      <c r="P4" s="51"/>
+      <c r="Q4" s="51"/>
+      <c r="R4" s="51"/>
+      <c r="S4" s="51"/>
+      <c r="T4" s="51"/>
+      <c r="U4" s="51"/>
+      <c r="V4" s="51"/>
+      <c r="W4" s="51"/>
+      <c r="X4" s="51"/>
+      <c r="Y4" s="51"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A5" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="52"/>
-      <c r="N5" s="52"/>
-      <c r="O5" s="52"/>
-      <c r="P5" s="52"/>
-      <c r="Q5" s="52"/>
-      <c r="R5" s="52"/>
-      <c r="S5" s="52"/>
-      <c r="T5" s="52"/>
-      <c r="U5" s="52"/>
-      <c r="V5" s="52"/>
-      <c r="W5" s="52"/>
-      <c r="X5" s="52"/>
-      <c r="Y5" s="52"/>
+      <c r="B5" s="51"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="51"/>
+      <c r="E5" s="51"/>
+      <c r="F5" s="51"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="51"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="51"/>
+      <c r="M5" s="51"/>
+      <c r="N5" s="51"/>
+      <c r="O5" s="51"/>
+      <c r="P5" s="51"/>
+      <c r="Q5" s="51"/>
+      <c r="R5" s="51"/>
+      <c r="S5" s="51"/>
+      <c r="T5" s="51"/>
+      <c r="U5" s="51"/>
+      <c r="V5" s="51"/>
+      <c r="W5" s="51"/>
+      <c r="X5" s="51"/>
+      <c r="Y5" s="51"/>
     </row>
     <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1628,93 +1637,93 @@
       <c r="Y6" s="1"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="54" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="B7" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="38"/>
-      <c r="D7" s="43" t="s">
+      <c r="C7" s="58"/>
+      <c r="D7" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="44"/>
-      <c r="F7" s="47" t="s">
+      <c r="E7" s="64"/>
+      <c r="F7" s="66" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="48"/>
-      <c r="K7" s="48"/>
-      <c r="L7" s="48"/>
-      <c r="M7" s="48"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="49"/>
-      <c r="P7" s="50" t="s">
+      <c r="G7" s="67"/>
+      <c r="H7" s="67"/>
+      <c r="I7" s="67"/>
+      <c r="J7" s="67"/>
+      <c r="K7" s="67"/>
+      <c r="L7" s="67"/>
+      <c r="M7" s="67"/>
+      <c r="N7" s="67"/>
+      <c r="O7" s="68"/>
+      <c r="P7" s="69" t="s">
         <v>7</v>
       </c>
-      <c r="Q7" s="48"/>
-      <c r="R7" s="48"/>
-      <c r="S7" s="48"/>
-      <c r="T7" s="48"/>
-      <c r="U7" s="48"/>
-      <c r="V7" s="48"/>
-      <c r="W7" s="49"/>
-      <c r="X7" s="54" t="s">
+      <c r="Q7" s="67"/>
+      <c r="R7" s="67"/>
+      <c r="S7" s="67"/>
+      <c r="T7" s="67"/>
+      <c r="U7" s="67"/>
+      <c r="V7" s="67"/>
+      <c r="W7" s="68"/>
+      <c r="X7" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="55"/>
+      <c r="Y7" s="39"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8" s="35"/>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="57" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="59"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="65"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="58"/>
-      <c r="H8" s="59" t="s">
+      <c r="G8" s="43"/>
+      <c r="H8" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="58"/>
-      <c r="J8" s="60" t="s">
+      <c r="I8" s="43"/>
+      <c r="J8" s="45" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="58"/>
-      <c r="L8" s="60" t="s">
+      <c r="K8" s="43"/>
+      <c r="L8" s="45" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="58"/>
-      <c r="N8" s="60" t="s">
+      <c r="M8" s="43"/>
+      <c r="N8" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="61"/>
-      <c r="P8" s="62" t="s">
+      <c r="O8" s="46"/>
+      <c r="P8" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="Q8" s="58"/>
-      <c r="R8" s="63" t="s">
+      <c r="Q8" s="43"/>
+      <c r="R8" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="S8" s="58"/>
-      <c r="T8" s="64" t="s">
+      <c r="S8" s="43"/>
+      <c r="T8" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="U8" s="58"/>
-      <c r="V8" s="64" t="s">
+      <c r="U8" s="43"/>
+      <c r="V8" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="W8" s="61"/>
-      <c r="X8" s="56"/>
-      <c r="Y8" s="46"/>
+      <c r="W8" s="46"/>
+      <c r="X8" s="40"/>
+      <c r="Y8" s="41"/>
     </row>
     <row r="9" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="36"/>
-      <c r="B9" s="41"/>
-      <c r="C9" s="42"/>
+      <c r="A9" s="56"/>
+      <c r="B9" s="61"/>
+      <c r="C9" s="62"/>
       <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
@@ -1783,7 +1792,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="34" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1873,7 +1882,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11" s="69"/>
+      <c r="A11" s="35"/>
       <c r="B11" s="11" t="s">
         <v>21</v>
       </c>
@@ -1961,7 +1970,7 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12" s="70"/>
+      <c r="A12" s="36"/>
       <c r="B12" s="12" t="s">
         <v>22</v>
       </c>
@@ -2059,7 +2068,7 @@
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13" s="71" t="s">
+      <c r="A13" s="37" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="11" t="s">
@@ -2149,7 +2158,7 @@
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14" s="69"/>
+      <c r="A14" s="35"/>
       <c r="B14" s="11" t="s">
         <v>21</v>
       </c>
@@ -2237,7 +2246,7 @@
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15" s="70"/>
+      <c r="A15" s="36"/>
       <c r="B15" s="12" t="s">
         <v>22</v>
       </c>
@@ -2335,7 +2344,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="71" t="s">
+      <c r="A16" s="37" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -2425,7 +2434,7 @@
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="69"/>
+      <c r="A17" s="35"/>
       <c r="B17" s="11" t="s">
         <v>21</v>
       </c>
@@ -2513,7 +2522,7 @@
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="70"/>
+      <c r="A18" s="36"/>
       <c r="B18" s="12" t="s">
         <v>22</v>
       </c>
@@ -2611,7 +2620,7 @@
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="71" t="s">
+      <c r="A19" s="37" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -2701,7 +2710,7 @@
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="69"/>
+      <c r="A20" s="35"/>
       <c r="B20" s="11" t="s">
         <v>21</v>
       </c>
@@ -2789,7 +2798,7 @@
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A21" s="70"/>
+      <c r="A21" s="36"/>
       <c r="B21" s="12" t="s">
         <v>22</v>
       </c>
@@ -2887,7 +2896,7 @@
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A22" s="71" t="s">
+      <c r="A22" s="37" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -2977,7 +2986,7 @@
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="69"/>
+      <c r="A23" s="35"/>
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
@@ -3065,7 +3074,7 @@
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A24" s="70"/>
+      <c r="A24" s="36"/>
       <c r="B24" s="12" t="s">
         <v>22</v>
       </c>
@@ -3163,7 +3172,7 @@
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A25" s="71" t="s">
+      <c r="A25" s="37" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -3253,7 +3262,7 @@
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A26" s="69"/>
+      <c r="A26" s="35"/>
       <c r="B26" s="11" t="s">
         <v>21</v>
       </c>
@@ -3341,7 +3350,7 @@
       </c>
     </row>
     <row r="27" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="70"/>
+      <c r="A27" s="36"/>
       <c r="B27" s="16" t="s">
         <v>22</v>
       </c>
@@ -3439,7 +3448,7 @@
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A28" s="65" t="s">
+      <c r="A28" s="31" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="26" t="s">
@@ -3539,7 +3548,7 @@
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="66"/>
+      <c r="A29" s="32"/>
       <c r="B29" s="28" t="s">
         <v>21</v>
       </c>
@@ -3637,7 +3646,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="67"/>
+      <c r="A30" s="33"/>
       <c r="B30" s="30" t="s">
         <v>22</v>
       </c>
@@ -3790,12 +3799,12 @@
     </row>
     <row r="33" spans="1:25" s="23" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A33" s="22"/>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="70" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="31"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="31"/>
+      <c r="C33" s="70"/>
+      <c r="D33" s="70"/>
+      <c r="E33" s="70"/>
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
@@ -3806,12 +3815,12 @@
       <c r="M33" s="22"/>
       <c r="N33" s="22"/>
       <c r="O33" s="22"/>
-      <c r="P33" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q33" s="31"/>
-      <c r="R33" s="31"/>
-      <c r="S33" s="31"/>
+      <c r="P33" s="70" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q33" s="70"/>
+      <c r="R33" s="70"/>
+      <c r="S33" s="70"/>
       <c r="T33" s="22"/>
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
@@ -3821,12 +3830,12 @@
     </row>
     <row r="34" spans="1:25" s="23" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A34" s="22"/>
-      <c r="B34" s="32" t="s">
+      <c r="B34" s="71" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="32"/>
-      <c r="D34" s="32"/>
-      <c r="E34" s="32"/>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="71"/>
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
       <c r="H34" s="22"/>
@@ -3837,12 +3846,12 @@
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
       <c r="O34" s="22"/>
-      <c r="P34" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q34" s="32"/>
-      <c r="R34" s="32"/>
-      <c r="S34" s="32"/>
+      <c r="P34" s="71" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q34" s="71"/>
+      <c r="R34" s="71"/>
+      <c r="S34" s="71"/>
       <c r="T34" s="22"/>
       <c r="U34" s="22"/>
       <c r="V34" s="22"/>
@@ -3852,12 +3861,12 @@
     </row>
     <row r="35" spans="1:25" s="23" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A35" s="22"/>
-      <c r="B35" s="33" t="s">
+      <c r="B35" s="72" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="33"/>
-      <c r="D35" s="33"/>
-      <c r="E35" s="33"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
       <c r="F35" s="22"/>
       <c r="G35" s="22"/>
       <c r="H35" s="22"/>
@@ -3868,12 +3877,12 @@
       <c r="M35" s="22"/>
       <c r="N35" s="22"/>
       <c r="O35" s="22"/>
-      <c r="P35" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q35" s="33"/>
-      <c r="R35" s="33"/>
-      <c r="S35" s="33"/>
+      <c r="P35" s="72" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q35" s="72"/>
+      <c r="R35" s="72"/>
+      <c r="S35" s="72"/>
       <c r="T35" s="22"/>
       <c r="U35" s="22"/>
       <c r="V35" s="22"/>
@@ -29938,13 +29947,22 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="P33:S33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="P34:S34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="P35:S35"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:C9"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="P7:W7"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A3:Y3"/>
+    <mergeCell ref="A4:Y4"/>
+    <mergeCell ref="A5:Y5"/>
     <mergeCell ref="X7:Y8"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="H8:I8"/>
@@ -29955,22 +29973,13 @@
     <mergeCell ref="R8:S8"/>
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="V8:W8"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A3:Y3"/>
-    <mergeCell ref="A4:Y4"/>
-    <mergeCell ref="A5:Y5"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:C9"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="P7:W7"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="P33:S33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="P34:S34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="P35:S35"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>

--- a/public/exel/sns_highschool.xlsx
+++ b/public/exel/sns_highschool.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26626"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\sbfp_ao_system\public\exel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F727526-3107-4C64-8A49-C56540BE2C26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D56359AB-4853-4E90-BF27-DD404EE99F5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A97BA7C1-031B-4AE1-ABEF-59888A293735}"/>
   </bookViews>
@@ -135,6 +135,15 @@
     <t>NUTRITIONAL STATUS REPORT OF CANUBING NATIONAL HIGH SCHOOL</t>
   </si>
   <si>
+    <t>Approved by :</t>
+  </si>
+  <si>
+    <t>(School Head Nme)</t>
+  </si>
+  <si>
+    <t>School Head</t>
+  </si>
+  <si>
     <r>
       <t xml:space="preserve">Baseline (June) </t>
     </r>
@@ -147,17 +156,8 @@
         <rFont val="Tahoma"/>
         <family val="2"/>
       </rPr>
-      <t>SY  2025 -2026</t>
+      <t>SY  2026 -2027</t>
     </r>
-  </si>
-  <si>
-    <t>Approved by :</t>
-  </si>
-  <si>
-    <t>(School Head Nme)</t>
-  </si>
-  <si>
-    <t>School Head</t>
   </si>
 </sst>
 </file>
@@ -990,25 +990,57 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1029,50 +1061,18 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1465,149 +1465,149 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51"/>
-      <c r="H1" s="51"/>
-      <c r="I1" s="51"/>
-      <c r="J1" s="51"/>
-      <c r="K1" s="51"/>
-      <c r="L1" s="51"/>
-      <c r="M1" s="51"/>
-      <c r="N1" s="51"/>
-      <c r="O1" s="51"/>
-      <c r="P1" s="51"/>
-      <c r="Q1" s="51"/>
-      <c r="R1" s="51"/>
-      <c r="S1" s="51"/>
-      <c r="T1" s="51"/>
-      <c r="U1" s="51"/>
-      <c r="V1" s="51"/>
-      <c r="W1" s="51"/>
-      <c r="X1" s="51"/>
-      <c r="Y1" s="51"/>
+      <c r="A1" s="51" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="52"/>
+      <c r="C1" s="52"/>
+      <c r="D1" s="52"/>
+      <c r="E1" s="52"/>
+      <c r="F1" s="52"/>
+      <c r="G1" s="52"/>
+      <c r="H1" s="52"/>
+      <c r="I1" s="52"/>
+      <c r="J1" s="52"/>
+      <c r="K1" s="52"/>
+      <c r="L1" s="52"/>
+      <c r="M1" s="52"/>
+      <c r="N1" s="52"/>
+      <c r="O1" s="52"/>
+      <c r="P1" s="52"/>
+      <c r="Q1" s="52"/>
+      <c r="R1" s="52"/>
+      <c r="S1" s="52"/>
+      <c r="T1" s="52"/>
+      <c r="U1" s="52"/>
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="52"/>
+      <c r="Y1" s="52"/>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A2" s="50" t="s">
+      <c r="A2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="51"/>
-      <c r="K2" s="51"/>
-      <c r="L2" s="51"/>
-      <c r="M2" s="51"/>
-      <c r="N2" s="51"/>
-      <c r="O2" s="51"/>
-      <c r="P2" s="51"/>
-      <c r="Q2" s="51"/>
-      <c r="R2" s="51"/>
-      <c r="S2" s="51"/>
-      <c r="T2" s="51"/>
-      <c r="U2" s="51"/>
-      <c r="V2" s="51"/>
-      <c r="W2" s="51"/>
-      <c r="X2" s="51"/>
-      <c r="Y2" s="51"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+      <c r="D2" s="52"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="52"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="52"/>
+      <c r="L2" s="52"/>
+      <c r="M2" s="52"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="52"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="52"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="52"/>
+      <c r="T2" s="52"/>
+      <c r="U2" s="52"/>
+      <c r="V2" s="52"/>
+      <c r="W2" s="52"/>
+      <c r="X2" s="52"/>
+      <c r="Y2" s="52"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="51"/>
-      <c r="N3" s="51"/>
-      <c r="O3" s="51"/>
-      <c r="P3" s="51"/>
-      <c r="Q3" s="51"/>
-      <c r="R3" s="51"/>
-      <c r="S3" s="51"/>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
-      <c r="V3" s="51"/>
-      <c r="W3" s="51"/>
-      <c r="X3" s="51"/>
-      <c r="Y3" s="51"/>
+      <c r="B3" s="52"/>
+      <c r="C3" s="52"/>
+      <c r="D3" s="52"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="52"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="52"/>
+      <c r="O3" s="52"/>
+      <c r="P3" s="52"/>
+      <c r="Q3" s="52"/>
+      <c r="R3" s="52"/>
+      <c r="S3" s="52"/>
+      <c r="T3" s="52"/>
+      <c r="U3" s="52"/>
+      <c r="V3" s="52"/>
+      <c r="W3" s="52"/>
+      <c r="X3" s="52"/>
+      <c r="Y3" s="52"/>
     </row>
     <row r="4" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A4" s="52" t="s">
+      <c r="A4" s="53" t="s">
         <v>32</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="51"/>
-      <c r="N4" s="51"/>
-      <c r="O4" s="51"/>
-      <c r="P4" s="51"/>
-      <c r="Q4" s="51"/>
-      <c r="R4" s="51"/>
-      <c r="S4" s="51"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="51"/>
-      <c r="V4" s="51"/>
-      <c r="W4" s="51"/>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="51"/>
+      <c r="B4" s="52"/>
+      <c r="C4" s="52"/>
+      <c r="D4" s="52"/>
+      <c r="E4" s="52"/>
+      <c r="F4" s="52"/>
+      <c r="G4" s="52"/>
+      <c r="H4" s="52"/>
+      <c r="I4" s="52"/>
+      <c r="J4" s="52"/>
+      <c r="K4" s="52"/>
+      <c r="L4" s="52"/>
+      <c r="M4" s="52"/>
+      <c r="N4" s="52"/>
+      <c r="O4" s="52"/>
+      <c r="P4" s="52"/>
+      <c r="Q4" s="52"/>
+      <c r="R4" s="52"/>
+      <c r="S4" s="52"/>
+      <c r="T4" s="52"/>
+      <c r="U4" s="52"/>
+      <c r="V4" s="52"/>
+      <c r="W4" s="52"/>
+      <c r="X4" s="52"/>
+      <c r="Y4" s="52"/>
     </row>
     <row r="5" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A5" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="51"/>
-      <c r="F5" s="51"/>
-      <c r="G5" s="51"/>
-      <c r="H5" s="51"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="51"/>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="51"/>
-      <c r="W5" s="51"/>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="51"/>
+      <c r="A5" s="54" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="52"/>
+      <c r="K5" s="52"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="52"/>
+      <c r="N5" s="52"/>
+      <c r="O5" s="52"/>
+      <c r="P5" s="52"/>
+      <c r="Q5" s="52"/>
+      <c r="R5" s="52"/>
+      <c r="S5" s="52"/>
+      <c r="T5" s="52"/>
+      <c r="U5" s="52"/>
+      <c r="V5" s="52"/>
+      <c r="W5" s="52"/>
+      <c r="X5" s="52"/>
+      <c r="Y5" s="52"/>
     </row>
     <row r="6" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="1"/>
@@ -1637,93 +1637,93 @@
       <c r="Y6" s="1"/>
     </row>
     <row r="7" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="63" t="s">
+      <c r="C7" s="38"/>
+      <c r="D7" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="64"/>
-      <c r="F7" s="66" t="s">
+      <c r="E7" s="44"/>
+      <c r="F7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="G7" s="67"/>
-      <c r="H7" s="67"/>
-      <c r="I7" s="67"/>
-      <c r="J7" s="67"/>
-      <c r="K7" s="67"/>
-      <c r="L7" s="67"/>
-      <c r="M7" s="67"/>
-      <c r="N7" s="67"/>
-      <c r="O7" s="68"/>
-      <c r="P7" s="69" t="s">
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+      <c r="M7" s="48"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="49"/>
+      <c r="P7" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="Q7" s="67"/>
-      <c r="R7" s="67"/>
-      <c r="S7" s="67"/>
-      <c r="T7" s="67"/>
-      <c r="U7" s="67"/>
-      <c r="V7" s="67"/>
-      <c r="W7" s="68"/>
-      <c r="X7" s="38" t="s">
+      <c r="Q7" s="48"/>
+      <c r="R7" s="48"/>
+      <c r="S7" s="48"/>
+      <c r="T7" s="48"/>
+      <c r="U7" s="48"/>
+      <c r="V7" s="48"/>
+      <c r="W7" s="49"/>
+      <c r="X7" s="55" t="s">
         <v>8</v>
       </c>
-      <c r="Y7" s="39"/>
+      <c r="Y7" s="56"/>
     </row>
     <row r="8" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A8" s="55"/>
-      <c r="B8" s="59"/>
-      <c r="C8" s="60"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="42" t="s">
+      <c r="A8" s="35"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="58" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="43"/>
-      <c r="H8" s="44" t="s">
+      <c r="G8" s="59"/>
+      <c r="H8" s="60" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="43"/>
-      <c r="J8" s="45" t="s">
+      <c r="I8" s="59"/>
+      <c r="J8" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="K8" s="43"/>
-      <c r="L8" s="45" t="s">
+      <c r="K8" s="59"/>
+      <c r="L8" s="61" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="43"/>
-      <c r="N8" s="45" t="s">
+      <c r="M8" s="59"/>
+      <c r="N8" s="61" t="s">
         <v>13</v>
       </c>
-      <c r="O8" s="46"/>
-      <c r="P8" s="47" t="s">
+      <c r="O8" s="62"/>
+      <c r="P8" s="63" t="s">
         <v>14</v>
       </c>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="48" t="s">
+      <c r="Q8" s="59"/>
+      <c r="R8" s="64" t="s">
         <v>15</v>
       </c>
-      <c r="S8" s="43"/>
-      <c r="T8" s="49" t="s">
+      <c r="S8" s="59"/>
+      <c r="T8" s="65" t="s">
         <v>11</v>
       </c>
-      <c r="U8" s="43"/>
-      <c r="V8" s="49" t="s">
+      <c r="U8" s="59"/>
+      <c r="V8" s="65" t="s">
         <v>16</v>
       </c>
-      <c r="W8" s="46"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="41"/>
+      <c r="W8" s="62"/>
+      <c r="X8" s="57"/>
+      <c r="Y8" s="46"/>
     </row>
     <row r="9" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="56"/>
-      <c r="B9" s="61"/>
-      <c r="C9" s="62"/>
+      <c r="A9" s="36"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="42"/>
       <c r="D9" s="2" t="s">
         <v>17</v>
       </c>
@@ -1792,7 +1792,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" ht="15" thickTop="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="34" t="s">
+      <c r="A10" s="69" t="s">
         <v>19</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -1882,7 +1882,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A11" s="35"/>
+      <c r="A11" s="70"/>
       <c r="B11" s="11" t="s">
         <v>21</v>
       </c>
@@ -1970,7 +1970,7 @@
       </c>
     </row>
     <row r="12" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A12" s="36"/>
+      <c r="A12" s="71"/>
       <c r="B12" s="12" t="s">
         <v>22</v>
       </c>
@@ -2068,7 +2068,7 @@
       </c>
     </row>
     <row r="13" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="72" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="11" t="s">
@@ -2158,7 +2158,7 @@
       </c>
     </row>
     <row r="14" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A14" s="35"/>
+      <c r="A14" s="70"/>
       <c r="B14" s="11" t="s">
         <v>21</v>
       </c>
@@ -2246,7 +2246,7 @@
       </c>
     </row>
     <row r="15" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A15" s="36"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="12" t="s">
         <v>22</v>
       </c>
@@ -2344,7 +2344,7 @@
       </c>
     </row>
     <row r="16" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A16" s="37" t="s">
+      <c r="A16" s="72" t="s">
         <v>24</v>
       </c>
       <c r="B16" s="11" t="s">
@@ -2434,7 +2434,7 @@
       </c>
     </row>
     <row r="17" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A17" s="35"/>
+      <c r="A17" s="70"/>
       <c r="B17" s="11" t="s">
         <v>21</v>
       </c>
@@ -2522,7 +2522,7 @@
       </c>
     </row>
     <row r="18" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A18" s="36"/>
+      <c r="A18" s="71"/>
       <c r="B18" s="12" t="s">
         <v>22</v>
       </c>
@@ -2620,7 +2620,7 @@
       </c>
     </row>
     <row r="19" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A19" s="37" t="s">
+      <c r="A19" s="72" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="11" t="s">
@@ -2710,7 +2710,7 @@
       </c>
     </row>
     <row r="20" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A20" s="35"/>
+      <c r="A20" s="70"/>
       <c r="B20" s="11" t="s">
         <v>21</v>
       </c>
@@ -2798,7 +2798,7 @@
       </c>
     </row>
     <row r="21" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A21" s="36"/>
+      <c r="A21" s="71"/>
       <c r="B21" s="12" t="s">
         <v>22</v>
       </c>
@@ -2896,7 +2896,7 @@
       </c>
     </row>
     <row r="22" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A22" s="37" t="s">
+      <c r="A22" s="72" t="s">
         <v>26</v>
       </c>
       <c r="B22" s="11" t="s">
@@ -2986,7 +2986,7 @@
       </c>
     </row>
     <row r="23" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A23" s="35"/>
+      <c r="A23" s="70"/>
       <c r="B23" s="11" t="s">
         <v>21</v>
       </c>
@@ -3074,7 +3074,7 @@
       </c>
     </row>
     <row r="24" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A24" s="36"/>
+      <c r="A24" s="71"/>
       <c r="B24" s="12" t="s">
         <v>22</v>
       </c>
@@ -3172,7 +3172,7 @@
       </c>
     </row>
     <row r="25" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A25" s="37" t="s">
+      <c r="A25" s="72" t="s">
         <v>27</v>
       </c>
       <c r="B25" s="11" t="s">
@@ -3262,7 +3262,7 @@
       </c>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A26" s="35"/>
+      <c r="A26" s="70"/>
       <c r="B26" s="11" t="s">
         <v>21</v>
       </c>
@@ -3350,7 +3350,7 @@
       </c>
     </row>
     <row r="27" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A27" s="36"/>
+      <c r="A27" s="71"/>
       <c r="B27" s="16" t="s">
         <v>22</v>
       </c>
@@ -3448,7 +3448,7 @@
       </c>
     </row>
     <row r="28" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="66" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="26" t="s">
@@ -3548,7 +3548,7 @@
       </c>
     </row>
     <row r="29" spans="1:25" x14ac:dyDescent="0.35">
-      <c r="A29" s="32"/>
+      <c r="A29" s="67"/>
       <c r="B29" s="28" t="s">
         <v>21</v>
       </c>
@@ -3646,7 +3646,7 @@
       </c>
     </row>
     <row r="30" spans="1:25" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A30" s="33"/>
+      <c r="A30" s="68"/>
       <c r="B30" s="30" t="s">
         <v>22</v>
       </c>
@@ -3799,12 +3799,12 @@
     </row>
     <row r="33" spans="1:25" s="23" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A33" s="22"/>
-      <c r="B33" s="70" t="s">
+      <c r="B33" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="C33" s="70"/>
-      <c r="D33" s="70"/>
-      <c r="E33" s="70"/>
+      <c r="C33" s="31"/>
+      <c r="D33" s="31"/>
+      <c r="E33" s="31"/>
       <c r="F33" s="22"/>
       <c r="G33" s="22"/>
       <c r="H33" s="22"/>
@@ -3815,12 +3815,12 @@
       <c r="M33" s="22"/>
       <c r="N33" s="22"/>
       <c r="O33" s="22"/>
-      <c r="P33" s="70" t="s">
-        <v>34</v>
-      </c>
-      <c r="Q33" s="70"/>
-      <c r="R33" s="70"/>
-      <c r="S33" s="70"/>
+      <c r="P33" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="31"/>
+      <c r="S33" s="31"/>
       <c r="T33" s="22"/>
       <c r="U33" s="22"/>
       <c r="V33" s="22"/>
@@ -3830,12 +3830,12 @@
     </row>
     <row r="34" spans="1:25" s="23" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A34" s="22"/>
-      <c r="B34" s="71" t="s">
+      <c r="B34" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="71"/>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32"/>
       <c r="F34" s="22"/>
       <c r="G34" s="22"/>
       <c r="H34" s="22"/>
@@ -3846,12 +3846,12 @@
       <c r="M34" s="22"/>
       <c r="N34" s="22"/>
       <c r="O34" s="22"/>
-      <c r="P34" s="71" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q34" s="71"/>
-      <c r="R34" s="71"/>
-      <c r="S34" s="71"/>
+      <c r="P34" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q34" s="32"/>
+      <c r="R34" s="32"/>
+      <c r="S34" s="32"/>
       <c r="T34" s="22"/>
       <c r="U34" s="22"/>
       <c r="V34" s="22"/>
@@ -3861,12 +3861,12 @@
     </row>
     <row r="35" spans="1:25" s="23" customFormat="1" ht="12" x14ac:dyDescent="0.3">
       <c r="A35" s="22"/>
-      <c r="B35" s="72" t="s">
+      <c r="B35" s="33" t="s">
         <v>31</v>
       </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="33"/>
+      <c r="E35" s="33"/>
       <c r="F35" s="22"/>
       <c r="G35" s="22"/>
       <c r="H35" s="22"/>
@@ -3877,12 +3877,12 @@
       <c r="M35" s="22"/>
       <c r="N35" s="22"/>
       <c r="O35" s="22"/>
-      <c r="P35" s="72" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q35" s="72"/>
-      <c r="R35" s="72"/>
-      <c r="S35" s="72"/>
+      <c r="P35" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q35" s="33"/>
+      <c r="R35" s="33"/>
+      <c r="S35" s="33"/>
       <c r="T35" s="22"/>
       <c r="U35" s="22"/>
       <c r="V35" s="22"/>
@@ -29947,22 +29947,13 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="P33:S33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="P34:S34"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="P35:S35"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:C9"/>
-    <mergeCell ref="D7:E8"/>
-    <mergeCell ref="F7:O7"/>
-    <mergeCell ref="P7:W7"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A2:Y2"/>
-    <mergeCell ref="A3:Y3"/>
-    <mergeCell ref="A4:Y4"/>
-    <mergeCell ref="A5:Y5"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A25:A27"/>
     <mergeCell ref="X7:Y8"/>
     <mergeCell ref="F8:G8"/>
     <mergeCell ref="H8:I8"/>
@@ -29973,13 +29964,22 @@
     <mergeCell ref="R8:S8"/>
     <mergeCell ref="T8:U8"/>
     <mergeCell ref="V8:W8"/>
-    <mergeCell ref="A28:A30"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A1:Y1"/>
+    <mergeCell ref="A2:Y2"/>
+    <mergeCell ref="A3:Y3"/>
+    <mergeCell ref="A4:Y4"/>
+    <mergeCell ref="A5:Y5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="B7:C9"/>
+    <mergeCell ref="D7:E8"/>
+    <mergeCell ref="F7:O7"/>
+    <mergeCell ref="P7:W7"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="P33:S33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="P34:S34"/>
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="P35:S35"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
